--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260616_220810.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
